--- a/artfynd/A 29866-2023 artfynd.xlsx
+++ b/artfynd/A 29866-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29866-2023 artfynd.xlsx
+++ b/artfynd/A 29866-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>

--- a/artfynd/A 29866-2023 artfynd.xlsx
+++ b/artfynd/A 29866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112221323</v>
+        <v>112221011</v>
       </c>
       <c r="B2" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617927</v>
+        <v>617996</v>
       </c>
       <c r="R2" t="n">
-        <v>7265495</v>
+        <v>7265516</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,17 +751,13 @@
           <t>2023-09-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspettskalad gren på  undervegetationsgrsn. Tretå observerad födosökande nära liksom Ringhack. Allra mest troligt tretå</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112221873</v>
+        <v>112254521</v>
       </c>
       <c r="B3" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617699</v>
+        <v>617624</v>
       </c>
       <c r="R3" t="n">
-        <v>7265465</v>
+        <v>7265452</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112221174</v>
+        <v>112221170</v>
       </c>
       <c r="B4" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1002,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112220995</v>
+        <v>112254474</v>
       </c>
       <c r="B5" t="n">
-        <v>88676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618001</v>
+        <v>617593</v>
       </c>
       <c r="R5" t="n">
-        <v>7265521</v>
+        <v>7265453</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1108,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112220991</v>
+        <v>112254411</v>
       </c>
       <c r="B6" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618001</v>
+        <v>617579</v>
       </c>
       <c r="R6" t="n">
-        <v>7265521</v>
+        <v>7265423</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112221165</v>
+        <v>112254477</v>
       </c>
       <c r="B7" t="n">
-        <v>88676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>617967</v>
+        <v>617593</v>
       </c>
       <c r="R7" t="n">
-        <v>7265496</v>
+        <v>7265453</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112220975</v>
+        <v>112220995</v>
       </c>
       <c r="B8" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618020</v>
+        <v>618000</v>
       </c>
       <c r="R8" t="n">
-        <v>7265521</v>
+        <v>7265522</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112221397</v>
+        <v>112221165</v>
       </c>
       <c r="B9" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1442,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>617945</v>
+        <v>617967</v>
       </c>
       <c r="R9" t="n">
-        <v>7265470</v>
+        <v>7265496</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112221143</v>
+        <v>112221233</v>
       </c>
       <c r="B10" t="n">
-        <v>90869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,7 +1521,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>617972</v>
+        <v>617941</v>
       </c>
       <c r="R10" t="n">
         <v>7265508</v>
@@ -1638,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112221380</v>
+        <v>112254531</v>
       </c>
       <c r="B11" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>617952</v>
+        <v>617635</v>
       </c>
       <c r="R11" t="n">
-        <v>7265480</v>
+        <v>7265444</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1744,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112221170</v>
+        <v>112254542</v>
       </c>
       <c r="B12" t="n">
-        <v>77360</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>617967</v>
+        <v>617642</v>
       </c>
       <c r="R12" t="n">
-        <v>7265496</v>
+        <v>7265457</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1850,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112221233</v>
+        <v>112254571</v>
       </c>
       <c r="B13" t="n">
-        <v>88676</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>617942</v>
+        <v>617654</v>
       </c>
       <c r="R13" t="n">
-        <v>7265508</v>
+        <v>7265480</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1956,56 +1887,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112221011</v>
+        <v>113886420</v>
       </c>
       <c r="B14" t="n">
-        <v>89833</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>617996</v>
+        <v>617919</v>
       </c>
       <c r="R14" t="n">
-        <v>7265516</v>
+        <v>7265501</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,12 +1956,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2043,66 +1975,55 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112254423</v>
+        <v>112221143</v>
       </c>
       <c r="B15" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2110,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>617579</v>
+        <v>617972</v>
       </c>
       <c r="R15" t="n">
-        <v>7265423</v>
+        <v>7265508</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2154,6 +2075,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2172,56 +2094,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112254508</v>
+        <v>113887620</v>
       </c>
       <c r="B16" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>617619</v>
+        <v>617569</v>
       </c>
       <c r="R16" t="n">
-        <v>7265451</v>
+        <v>7265321</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2245,12 +2163,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2259,34 +2182,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112254479</v>
+        <v>112254540</v>
       </c>
       <c r="B17" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2321,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>617593</v>
+        <v>617642</v>
       </c>
       <c r="R17" t="n">
-        <v>7265453</v>
+        <v>7265457</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2384,15 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112254450</v>
+        <v>112220975</v>
       </c>
       <c r="B18" t="n">
-        <v>56461</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,31 +2312,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2432,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>617583</v>
+        <v>618020</v>
       </c>
       <c r="R18" t="n">
-        <v>7265437</v>
+        <v>7265520</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2470,17 +2377,13 @@
           <t>2023-09-17</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack 3 meter från avverkningsplanerad skog</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2499,15 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112254531</v>
+        <v>112254508</v>
       </c>
       <c r="B19" t="n">
-        <v>88678</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>617635</v>
+        <v>617619</v>
       </c>
       <c r="R19" t="n">
-        <v>7265444</v>
+        <v>7265451</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2605,57 +2503,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112254661</v>
+        <v>113886927</v>
       </c>
       <c r="B20" t="n">
-        <v>56568</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>617729</v>
+        <v>617917</v>
       </c>
       <c r="R20" t="n">
-        <v>7265487</v>
+        <v>7265497</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2679,12 +2572,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,27 +2597,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112254546</v>
+        <v>113886968</v>
       </c>
       <c r="B21" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,45 +2620,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>617642</v>
+        <v>617620</v>
       </c>
       <c r="R21" t="n">
-        <v>7265457</v>
+        <v>7265461</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2789,12 +2678,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,27 +2703,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112254491</v>
+        <v>113887766</v>
       </c>
       <c r="B22" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,40 +2726,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>617619</v>
+        <v>617950</v>
       </c>
       <c r="R22" t="n">
-        <v>7265460</v>
+        <v>7265496</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2894,12 +2784,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2908,34 +2803,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112254523</v>
+        <v>113887767</v>
       </c>
       <c r="B23" t="n">
-        <v>56606</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,45 +2832,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>617624</v>
+        <v>617644</v>
       </c>
       <c r="R23" t="n">
-        <v>7265452</v>
+        <v>7265449</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3005,12 +2890,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,77 +2915,64 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112254640</v>
+        <v>113887791</v>
       </c>
       <c r="B24" t="n">
-        <v>55682</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>617693</v>
+        <v>617915</v>
       </c>
       <c r="R24" t="n">
-        <v>7265510</v>
+        <v>7265482</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,17 +2996,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Stjärtfjäder från tjädertupp</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,27 +3021,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112254375</v>
+        <v>113887792</v>
       </c>
       <c r="B25" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,40 +3044,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>617583</v>
+        <v>617655</v>
       </c>
       <c r="R25" t="n">
-        <v>7265393</v>
+        <v>7265444</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3229,12 +3102,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,75 +3121,70 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112254411</v>
+        <v>113887502</v>
       </c>
       <c r="B26" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>617579</v>
+        <v>617920</v>
       </c>
       <c r="R26" t="n">
-        <v>7265423</v>
+        <v>7265500</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3335,12 +3208,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3349,75 +3227,70 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112254521</v>
+        <v>113888791</v>
       </c>
       <c r="B27" t="n">
-        <v>89835</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spänningsberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>617624</v>
+        <v>617670</v>
       </c>
       <c r="R27" t="n">
-        <v>7265452</v>
+        <v>7265510</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3441,12 +3314,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3455,56 +3333,50 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112254658</v>
+        <v>112221896</v>
       </c>
       <c r="B28" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>617729</v>
+        <v>617552</v>
       </c>
       <c r="R28" t="n">
-        <v>7265487</v>
+        <v>7265418</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3547,12 +3419,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,37 +3452,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112254542</v>
+        <v>112254375</v>
       </c>
       <c r="B29" t="n">
-        <v>88678</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3623,10 +3490,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>617642</v>
+        <v>617583</v>
       </c>
       <c r="R29" t="n">
-        <v>7265457</v>
+        <v>7265393</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3686,15 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112254571</v>
+        <v>112220991</v>
       </c>
       <c r="B30" t="n">
-        <v>88678</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,21 +3564,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>617653</v>
+        <v>618000</v>
       </c>
       <c r="R30" t="n">
-        <v>7265480</v>
+        <v>7265522</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3792,15 +3654,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112254622</v>
+        <v>112221174</v>
       </c>
       <c r="B31" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3835,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>617693</v>
+        <v>617967</v>
       </c>
       <c r="R31" t="n">
-        <v>7265510</v>
+        <v>7265496</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,15 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112254540</v>
+        <v>112254491</v>
       </c>
       <c r="B32" t="n">
-        <v>91043</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3914,21 +3766,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3941,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>617642</v>
+        <v>617618</v>
       </c>
       <c r="R32" t="n">
-        <v>7265457</v>
+        <v>7265460</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4004,15 +3856,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112254477</v>
+        <v>112254622</v>
       </c>
       <c r="B33" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4020,21 +3867,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4047,10 +3894,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>617593</v>
+        <v>617693</v>
       </c>
       <c r="R33" t="n">
-        <v>7265453</v>
+        <v>7265510</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4110,15 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112254591</v>
+        <v>112254658</v>
       </c>
       <c r="B34" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4126,21 +3968,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>617661</v>
+        <v>617729</v>
       </c>
       <c r="R34" t="n">
-        <v>7265491</v>
+        <v>7265487</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4216,42 +4058,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112254474</v>
+        <v>112221771</v>
       </c>
       <c r="B35" t="n">
-        <v>89875</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4259,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>617593</v>
+        <v>617735</v>
       </c>
       <c r="R35" t="n">
-        <v>7265453</v>
+        <v>7265274</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4289,12 +4127,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4146,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4322,15 +4164,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113887791</v>
+        <v>112254423</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4338,41 +4175,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>617915</v>
+        <v>617579</v>
       </c>
       <c r="R36" t="n">
-        <v>7265482</v>
+        <v>7265423</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4396,17 +4237,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4421,27 +4257,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113886927</v>
+        <v>112221323</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,41 +4280,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>617917</v>
+        <v>617926</v>
       </c>
       <c r="R37" t="n">
-        <v>7265497</v>
+        <v>7265495</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4507,24 +4342,24 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>hackspettskalad gren på  undervegetationsgrsn. Tretå observerad födosökande nära liksom Ringhack. Allra mest troligt tretå</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4532,69 +4367,68 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113888791</v>
+        <v>112221892</v>
       </c>
       <c r="B38" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>617670</v>
+        <v>617552</v>
       </c>
       <c r="R38" t="n">
-        <v>7265510</v>
+        <v>7265418</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4618,17 +4452,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4643,27 +4472,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113886968</v>
+        <v>112254450</v>
       </c>
       <c r="B39" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4671,41 +4495,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>617620</v>
+        <v>617583</v>
       </c>
       <c r="R39" t="n">
-        <v>7265461</v>
+        <v>7265437</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4729,17 +4557,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Färska ringhack 3 meter från avverkningsplanerad skog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4754,69 +4582,72 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113886420</v>
+        <v>112254640</v>
       </c>
       <c r="B40" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>617919</v>
+        <v>617693</v>
       </c>
       <c r="R40" t="n">
-        <v>7265501</v>
+        <v>7265510</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4840,17 +4671,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Stjärtfjäder från tjädertupp</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,69 +4696,64 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113887620</v>
+        <v>112254392</v>
       </c>
       <c r="B41" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningberget, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>617569</v>
+        <v>617580</v>
       </c>
       <c r="R41" t="n">
-        <v>7265321</v>
+        <v>7265412</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4951,17 +4777,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,69 +4797,64 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113887502</v>
+        <v>112221873</v>
       </c>
       <c r="B42" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>617920</v>
+        <v>617700</v>
       </c>
       <c r="R42" t="n">
-        <v>7265500</v>
+        <v>7265465</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5062,17 +4878,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,69 +4898,68 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113887792</v>
+        <v>112254523</v>
       </c>
       <c r="B43" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>617655</v>
+        <v>617624</v>
       </c>
       <c r="R43" t="n">
-        <v>7265444</v>
+        <v>7265452</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5173,17 +4983,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5198,69 +5003,68 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113887767</v>
+        <v>112254546</v>
       </c>
       <c r="B44" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>617644</v>
+        <v>617642</v>
       </c>
       <c r="R44" t="n">
-        <v>7265449</v>
+        <v>7265457</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5284,17 +5088,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5309,69 +5108,72 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113887766</v>
+        <v>112221541</v>
       </c>
       <c r="B45" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Spänningsberget, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>617950</v>
+        <v>617958</v>
       </c>
       <c r="R45" t="n">
-        <v>7265496</v>
+        <v>7265508</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5395,17 +5197,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5420,15 +5217,419 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112254661</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Spänningsberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>617729</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7265487</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>112221380</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Spänningsberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>617952</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7265480</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>112221397</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Spänningsberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>617945</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7265470</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112254591</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Spänningsberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>617661</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7265491</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29866-2023 artfynd.xlsx
+++ b/artfynd/A 29866-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221011</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221170</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254474</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254411</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254477</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221165</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221233</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254531</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254542</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254571</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886420</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221143</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887620</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254540</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2399,6 +2484,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220975</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254508</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886927</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886968</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2818,6 +2923,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887766</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887767</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3030,6 +3145,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887791</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887792</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887502</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888791</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3449,6 +3584,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221896</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3550,6 +3690,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254375</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3651,6 +3796,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220991</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221174</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3853,6 +4008,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254491</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254622</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4055,6 +4220,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254658</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4161,6 +4331,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221771</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4266,6 +4441,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254423</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4376,6 +4556,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221323</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4481,6 +4666,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221892</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4591,6 +4781,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254450</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4705,6 +4900,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254640</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4806,6 +5006,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254392</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4907,6 +5112,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221873</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5012,6 +5222,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254523</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5117,6 +5332,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254546</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5226,6 +5446,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221541</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5327,6 +5552,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254661</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5428,6 +5658,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221380</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5529,6 +5764,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112221397</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5630,8 +5870,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254591</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>